--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>987.23</v>
+        <v>977.38</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>817.58</v>
+        <v>809.42</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2078.27</v>
+        <v>2085.11</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>872.95</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10681.54</v>
+        <v>10731.29</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>68602.78999999999</v>
+        <v>68922.28</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13043.6</v>
+        <v>12988.92</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2300.58</v>
+        <v>2283.37</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1712.69</v>
+        <v>1721.54</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5527.02</v>
+        <v>5577.29</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4237.24</v>
+        <v>4265.15</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1350.11</v>
+        <v>1362.13</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>42242.52</v>
+        <v>42012.48</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>30902.38</v>
+        <v>30734.1</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8115.48</v>
+        <v>8066.17</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4793.77</v>
+        <v>4812.67</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2118.24</v>
+        <v>2123.45</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3806.25</v>
+        <v>3806.05</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11247.21</v>
+        <v>11196.92</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2072.36</v>
+        <v>2066.65</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2205.96</v>
+        <v>2199.88</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1665.22</v>
+        <v>1660.63</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36868.09</v>
+        <v>36442.47</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>48007.49</v>
+        <v>47453.27</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9362.620000000001</v>
+        <v>9308.84</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>798.89</v>
+        <v>801.21</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>888.63</v>
+        <v>892.99</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1124.94</v>
+        <v>1130.47</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1346.14</v>
+        <v>1350.61</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>813.48</v>
+        <v>816.66</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8610.370000000001</v>
+        <v>8696.969999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5258.19</v>
+        <v>5293.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1038-264-CM25</t>
+          <t>3166-182-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.197.550-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>977.38</v>
+        <v>1045.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4627-31-CM25</t>
+          <t>707427-72-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>809.42</v>
+        <v>891.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4305-185-CM25</t>
+          <t>1038-264-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>78.197.550-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2085.11</v>
+        <v>977.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4305-189-CM25</t>
+          <t>4627-31-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>879</v>
+        <v>809.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3412-233-CM25</t>
+          <t>4305-185-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10731.29</v>
+        <v>2085.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1070-229-CM25</t>
+          <t>4305-189-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>68922.28</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1096-144-CM25</t>
+          <t>3412-233-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12988.92</v>
+        <v>10731.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2661-2-CM26</t>
+          <t>1070-229-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2283.37</v>
+        <v>68922.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4305-16-CM26</t>
+          <t>1096-144-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1721.54</v>
+        <v>12988.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3197-16-CM26</t>
+          <t>2661-2-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.962.600-1</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO WILLIAMS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALTA VISTA PRODUCCIONES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.037.029-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5577.29</v>
+        <v>2283.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3166-43-CM26</t>
+          <t>4305-16-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4265.15</v>
+        <v>1721.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3166-54-CM26</t>
+          <t>3197-16-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.962.600-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>GOBERNACION MARITIMA DE PUERTO WILLIAMS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>ALTA VISTA PRODUCCIONES SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.037.029-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1362.13</v>
+        <v>5577.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1069-5-CM26</t>
+          <t>3166-43-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>42012.48</v>
+        <v>4265.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1069-7-CM26</t>
+          <t>3166-54-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>30734.1</v>
+        <v>1362.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1030-20-CM26</t>
+          <t>1069-5-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8066.17</v>
+        <v>42012.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1069-13-CM26</t>
+          <t>1069-7-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4812.67</v>
+        <v>30734.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5147-45-CM26</t>
+          <t>1030-20-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2123.45</v>
+        <v>8066.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3704-55-CM26</t>
+          <t>1069-13-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3806.05</v>
+        <v>4812.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2663-126-CM26</t>
+          <t>5147-45-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11196.92</v>
+        <v>2123.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1000813-45-CM26</t>
+          <t>3704-55-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.197.550-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2066.65</v>
+        <v>3806.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1000813-46-CM26</t>
+          <t>2663-126-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.197.550-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2199.88</v>
+        <v>11196.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1000813-47-CM26</t>
+          <t>1000813-45-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1660.63</v>
+        <v>2066.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1070-34-CM26</t>
+          <t>1000813-46-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.197.550-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36442.47</v>
+        <v>2199.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1070-35-CM26</t>
+          <t>1000813-47-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.197.550-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>47453.27</v>
+        <v>1660.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1069-21-CM26</t>
+          <t>1070-35-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9308.84</v>
+        <v>47453.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1000813-84-CM26</t>
+          <t>1070-34-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.197.550-8</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>801.21</v>
+        <v>36442.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1000813-169-CM26</t>
+          <t>1069-21-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.197.550-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>892.99</v>
+        <v>9308.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1000813-181-CM26</t>
+          <t>1000813-84-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1130.47</v>
+        <v>801.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1805-19-CM26</t>
+          <t>1000813-169-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1350.61</v>
+        <v>892.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1000813-271-CM26</t>
+          <t>1000813-181-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>816.66</v>
+        <v>1130.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4305-80-CM26</t>
+          <t>1805-19-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>78.197.550-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8696.969999999999</v>
+        <v>1350.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1116007-99-CM26</t>
+          <t>1000813-271-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>78.197.550-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,6 +2460,128 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>816.66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4305-80-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.943.400-5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>8696.969999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1116007-99-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>5293.38</v>
       </c>
     </row>
